--- a/Result/profitability/3609.xlsx
+++ b/Result/profitability/3609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5337499999999999</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>19.4575</v>
+        <v>20.30875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.68</v>
+        <v>0.73875</v>
       </c>
       <c r="N3" t="n">
-        <v>20.1375</v>
+        <v>20.445</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8425</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>20.935</v>
+        <v>22.8375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.9875</v>
       </c>
       <c r="N5" t="n">
-        <v>23.72</v>
+        <v>24.89625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,13 +1139,13 @@
         <v>0.86</v>
       </c>
       <c r="M6" t="n">
-        <v>1.19875</v>
+        <v>-0.06124999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>20.6675</v>
+        <v>22.93125</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08750000000000004</v>
+        <v>0.09625000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>24.44</v>
+        <v>26.93375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.25625</v>
+        <v>0.2837500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>27.68</v>
+        <v>28.045</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>-0.03</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3837500000000001</v>
+        <v>0.38375</v>
       </c>
       <c r="N9" t="n">
         <v>27.9825</v>
@@ -9580,6 +9580,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3609</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>96</v>
+      </c>
+      <c r="D73" t="n">
+        <v>69</v>
+      </c>
+      <c r="E73" t="n">
+        <v>27</v>
+      </c>
+      <c r="F73" t="n">
+        <v>28</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-30.97%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-32</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-32</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.26375</v>
+      </c>
+      <c r="N73" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.2200000000000001</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.2095238095238096</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>2.920000000000002</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.1164274322169059</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.2200000000000001</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.2095238095238096</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.5061861215707371</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
